--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_07-10-2025.xlsx
@@ -539,17 +539,17 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>Regular price
-                  £10.30</t>
+                  £10.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.30</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.30</t>
+          <t>£10.00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -661,17 +661,17 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Regular price
-                  £11.60</t>
+                  £11.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.60</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.60</t>
+          <t>£11.30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -783,17 +783,17 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.05</t>
+                  £14.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£15.05</t>
+          <t>£14.60</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -905,17 +905,17 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>Regular price
-                  £15.35</t>
+                  £14.92</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.35</t>
+          <t>£14.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1027,17 +1027,17 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Regular price
-                  £19.52</t>
+                  £18.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.52</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.52</t>
+          <t>£18.99</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£19.18</t>
+          <t>£19.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1149,17 +1149,17 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.30</t>
+                  £20.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£21.30</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£21.30</t>
+          <t>£20.70</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1271,17 +1271,17 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Regular price
-                  £21.53</t>
+                  £20.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£21.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£21.53</t>
+          <t>£20.90</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1393,17 +1393,17 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Regular price
-                  £24.75</t>
+                  £23.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.95</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£24.75</t>
+          <t>£23.99</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1515,17 +1515,17 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.70</t>
+                  £25.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£26.70</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£26.70</t>
+          <t>£25.99</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£26.28</t>
+          <t>£26.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1637,17 +1637,17 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Regular price
-                  £26.40</t>
+                  £25.90</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.40</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£35.13</t>
+          <t>£35.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1881,17 +1881,17 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Regular price
-                  £32.25</t>
+                  £31.40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.25</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.25</t>
+          <t>£31.40</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£39.75</t>
+          <t>£40.06</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£39.00</t>
+          <t>£39.05</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2246,17 +2246,17 @@
       <c r="C16" t="inlineStr">
         <is>
           <t>Regular price
-                  £39.99</t>
+                  £38.30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£39.99</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£768.0</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>£984.0</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£29.45</t>
+          <t>£28.95</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£28.95</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£32.75</t>
+          <t>£28.95</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2708,17 +2708,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.60</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£38.75</t>
+          <t>£34.60</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£38.75</t>
+          <t>£34.60</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£43.60</t>
+          <t>£39.10</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>£40.21</t>
+          <t>£37.61</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£48.65</t>
+          <t>£43.59</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>£44.52</t>
+          <t>£42.87</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£43.99</t>
+          <t>£44.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£43.14</t>
+          <t>£43.29</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=140.0.7339.210); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7ab761eb5+80197]
-	GetHandleVerifier [0x0x7ff7ab761f10+80288]
-	(No symbol) [0x0x7ff7ab4e02fa]
-	(No symbol) [0x0x7ff7ab537cd7]
-	(No symbol) [0x0x7ff7ab537f9c]
-	(No symbol) [0x0x7ff7ab58ba87]
-	(No symbol) [0x0x7ff7ab5603bf]
-	(No symbol) [0x0x7ff7ab5887fb]
-	(No symbol) [0x0x7ff7ab560153]
-	(No symbol) [0x0x7ff7ab528b02]
-	(No symbol) [0x0x7ff7ab5298d3]
-	GetHandleVerifier [0x0x7ff7aba1e83d+2949837]
-	GetHandleVerifier [0x0x7ff7aba18c6a+2926330]
-	GetHandleVerifier [0x0x7ff7aba386c7+3055959]
-	GetHandleVerifier [0x0x7ff7ab77cfee+191102]
-	GetHandleVerifier [0x0x7ff7ab7850af+224063]
-	GetHandleVerifier [0x0x7ff7ab76af64+117236]
-	GetHandleVerifier [0x0x7ff7ab76b119+117673]
-	GetHandleVerifier [0x0x7ff7ab7510a8+11064]
+	GetHandleVerifier [0x0x7ff7f9f71eb5+80197]
+	GetHandleVerifier [0x0x7ff7f9f71f10+80288]
+	(No symbol) [0x0x7ff7f9cf02fa]
+	(No symbol) [0x0x7ff7f9d47cd7]
+	(No symbol) [0x0x7ff7f9d47f9c]
+	(No symbol) [0x0x7ff7f9d9ba87]
+	(No symbol) [0x0x7ff7f9d703bf]
+	(No symbol) [0x0x7ff7f9d987fb]
+	(No symbol) [0x0x7ff7f9d70153]
+	(No symbol) [0x0x7ff7f9d38b02]
+	(No symbol) [0x0x7ff7f9d398d3]
+	GetHandleVerifier [0x0x7ff7fa22e83d+2949837]
+	GetHandleVerifier [0x0x7ff7fa228c6a+2926330]
+	GetHandleVerifier [0x0x7ff7fa2486c7+3055959]
+	GetHandleVerifier [0x0x7ff7f9f8cfee+191102]
+	GetHandleVerifier [0x0x7ff7f9f950af+224063]
+	GetHandleVerifier [0x0x7ff7f9f7af64+117236]
+	GetHandleVerifier [0x0x7ff7f9f7b119+117673]
+	GetHandleVerifier [0x0x7ff7f9f610a8+11064]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>£1199.84</t>
+          <t>£1173.76</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>£1324.96</t>
+          <t>£1296.16</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
